--- a/Data/Variable Descriptions.xlsx
+++ b/Data/Variable Descriptions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowWidth="18352" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>ID</t>
   </si>
@@ -60,158 +60,19 @@
   <si>
     <t>log10-transformed GPT familiarity estimates</t>
   </si>
-  <si>
-    <t>Human_FAM_M_Su</t>
-  </si>
-  <si>
-    <t>human familiarity ratings from Su et al., 2022</t>
-  </si>
-  <si>
-    <t>Human_FAM_M_Su_log</t>
-  </si>
-  <si>
-    <t>log10-transformed human familiarity ratings from Su et al., 2022</t>
-  </si>
-  <si>
-    <t>zRT_LDT</t>
-  </si>
-  <si>
-    <t>standardized reaction time (zRT) for the Lexical Decision Task (LDT), from Tsang et al., 2018</t>
-  </si>
-  <si>
-    <t>ACC_LDT</t>
-  </si>
-  <si>
-    <t>accuracy for the Lexical Decision Task (LDT), from Tsang et al., 2018</t>
-  </si>
-  <si>
-    <t>NoS</t>
-  </si>
-  <si>
-    <t>average number of strokes of constituent characters in words</t>
-  </si>
-  <si>
-    <t>NoWF</t>
-  </si>
-  <si>
-    <t>log10-transformed average number of words formed by the constituent characters in words</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>log10-transformed average cumulative frequency of constituent characters in words</t>
-  </si>
-  <si>
-    <t>NoM</t>
-  </si>
-  <si>
-    <t>log10-transformed average number of meanings of the constituent characters in words</t>
-  </si>
-  <si>
-    <t>NoP</t>
-  </si>
-  <si>
-    <t>average number of pronunciations of the constituent characters in words</t>
-  </si>
-  <si>
-    <t>zRT_Nam_Liu</t>
-  </si>
-  <si>
-    <t>standardized reaction time (zRT) for the Word Naming Task (WNT), from Liu et al., 2007</t>
-  </si>
-  <si>
-    <t>zRT_Nam_Zhang</t>
-  </si>
-  <si>
-    <t>standardized reaction time (zRT) for the Word Naming Task (WNT), from Zhang et al., 2023</t>
-  </si>
-  <si>
-    <t>ACC_Nam_Zhang</t>
-  </si>
-  <si>
-    <t>accuracy for the Word Naming Task (WNT), from Zhang et al., 2023</t>
-  </si>
-  <si>
-    <t>AoA</t>
-  </si>
-  <si>
-    <t>average age-of-acquisition ratings of the words, from Xu et al., 2021</t>
-  </si>
-  <si>
-    <t>AoA_Liu</t>
-  </si>
-  <si>
-    <t>average age-of-acquisition ratings of the words, from Liu et al., 2007</t>
-  </si>
-  <si>
-    <t>SUBTLEX_logWF</t>
-  </si>
-  <si>
-    <t>log10-transformed word frequency of the words</t>
-  </si>
-  <si>
-    <t>SUBTLEX_logW_CD</t>
-  </si>
-  <si>
-    <t>log10-transformed contextual diversity of the words</t>
-  </si>
-  <si>
-    <t>Human_FAM_Liu</t>
-  </si>
-  <si>
-    <t>human familiarity ratings from Liu et al.,2007</t>
-  </si>
-  <si>
-    <t>GPT_FAM_probs_head</t>
-  </si>
-  <si>
-    <t>GPT familiarity estimates for the first character of the word</t>
-  </si>
-  <si>
-    <t>GPT_FAM_probs_head_log</t>
-  </si>
-  <si>
-    <t>log10-transformed GPT familiarity estimates for the first character of the word</t>
-  </si>
-  <si>
-    <t>SUBTLEX_logCHR_head</t>
-  </si>
-  <si>
-    <t>log10-transformed frequency of the first character</t>
-  </si>
-  <si>
-    <t>SUBTLEX_logCHR_CD_head</t>
-  </si>
-  <si>
-    <t>log10-transformed contextual diversity of the first character</t>
-  </si>
-  <si>
-    <t>zRT_Nam_Hendrix</t>
-  </si>
-  <si>
-    <t>standardized reaction time (zRT) for the Word Naming Task (WNT), from Hendrix et al., 2020</t>
-  </si>
-  <si>
-    <t>qwen_FAM_mean_30</t>
-  </si>
-  <si>
-    <t>Qwen-max familiarity estimates</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,12 +90,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -703,137 +558,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -847,12 +702,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1166,8 +1015,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="25.9380530973451" style="1" customWidth="1"/>
     <col min="2" max="2" width="116.008849557522" customWidth="1"/>
@@ -1213,190 +1062,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
